--- a/data/trans_dic/P11_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P11_R-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que el dolor le dificultó su trabajo habitual las últimas 4 semanas</t>
+          <t>Población a la que el dolor le dificultó su trabajo habitual las últimas 4 semanas (tasa de respuesta: 99,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>19,36; 30,33</t>
+          <t>19,32; 29,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16,01; 25,94</t>
+          <t>16,14; 25,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15,98; 25,85</t>
+          <t>16,08; 25,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23,49; 35,35</t>
+          <t>23,61; 35,81</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>29,53; 41,48</t>
+          <t>29,35; 41,03</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,53; 43,19</t>
+          <t>30,76; 42,79</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,32; 44,22</t>
+          <t>31,86; 43,77</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>45,07; 55,15</t>
+          <t>45,39; 55,32</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>25,83; 33,89</t>
+          <t>25,61; 33,86</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24,98; 32,56</t>
+          <t>25,1; 32,47</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25,26; 33,07</t>
+          <t>25,41; 33,16</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>35,8; 43,7</t>
+          <t>35,55; 43,32</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,04; 26,05</t>
+          <t>17,97; 25,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,13; 18,38</t>
+          <t>11,25; 18,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,31; 16,31</t>
+          <t>10,2; 16,02</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19,38; 27,71</t>
+          <t>18,89; 27,78</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>37,44; 46,3</t>
+          <t>38,03; 46,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,27; 33,34</t>
+          <t>25,28; 33,65</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,08; 25,63</t>
+          <t>17,94; 25,63</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>30,89; 38,42</t>
+          <t>31,17; 38,35</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>28,94; 34,85</t>
+          <t>28,77; 34,92</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18,96; 24,35</t>
+          <t>19,34; 24,67</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15,1; 19,8</t>
+          <t>15,02; 20,1</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>26,3; 31,86</t>
+          <t>26,08; 31,86</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,83; 17,01</t>
+          <t>9,8; 17,46</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,81; 20,71</t>
+          <t>11,99; 20,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,98; 17,23</t>
+          <t>10,01; 16,83</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>27,95; 37,72</t>
+          <t>27,55; 37,89</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>21,99; 31,64</t>
+          <t>22,56; 32,05</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21,8; 31,34</t>
+          <t>21,58; 31,69</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,76; 27,47</t>
+          <t>18,65; 28,23</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>32,36; 41,14</t>
+          <t>32,2; 40,6</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17,24; 23,66</t>
+          <t>16,81; 23,37</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18,06; 24,58</t>
+          <t>18,48; 24,76</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15,05; 21,31</t>
+          <t>15,26; 21,17</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>31,65; 38,28</t>
+          <t>31,42; 37,81</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,81; 25,97</t>
+          <t>16,61; 25,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,88; 20,73</t>
+          <t>13,73; 21,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,24; 26,92</t>
+          <t>18,02; 26,86</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25,23; 37,96</t>
+          <t>25,31; 37,14</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>29,96; 39,8</t>
+          <t>30,27; 40,08</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,9; 39,61</t>
+          <t>30,07; 39,65</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,38; 42,81</t>
+          <t>32,55; 43,2</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>20,43; 43,73</t>
+          <t>21,31; 43,6</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>24,89; 31,92</t>
+          <t>24,64; 31,23</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>22,79; 29,24</t>
+          <t>23,02; 29,6</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26,75; 33,36</t>
+          <t>26,69; 33,43</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>23,42; 38,95</t>
+          <t>24,19; 38,51</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,97; 20,12</t>
+          <t>10,95; 21,38</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,19; 27,93</t>
+          <t>16,01; 27,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16,7; 28,47</t>
+          <t>16,54; 28,6</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19,43; 29,07</t>
+          <t>18,95; 28,89</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>17,16; 29,58</t>
+          <t>17,79; 29,74</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>39,29; 52,84</t>
+          <t>39,93; 53,59</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,66; 35,75</t>
+          <t>23,28; 35,93</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>29,09; 37,86</t>
+          <t>29,24; 37,99</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>15,62; 23,49</t>
+          <t>15,58; 23,08</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29,8; 38,78</t>
+          <t>29,45; 38,83</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21,42; 29,95</t>
+          <t>21,81; 30,33</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>25,74; 32,24</t>
+          <t>25,69; 32,17</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14,52; 24,08</t>
+          <t>14,95; 23,53</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>19,9; 29,82</t>
+          <t>19,53; 29,86</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17,66; 28,21</t>
+          <t>17,21; 27,35</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>38,6; 49,17</t>
+          <t>38,71; 49,19</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>23,9; 35,41</t>
+          <t>24,79; 35,6</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>23,78; 34,75</t>
+          <t>23,56; 34,13</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>25,13; 36,75</t>
+          <t>25,33; 36,96</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>49,31; 59,75</t>
+          <t>49,65; 59,68</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>21,01; 28,2</t>
+          <t>20,88; 28,07</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>23,31; 31,27</t>
+          <t>23,6; 30,77</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>22,98; 30,56</t>
+          <t>22,68; 30,4</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>45,27; 52,77</t>
+          <t>45,22; 52,36</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>11,18; 16,81</t>
+          <t>11,47; 16,79</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12,27; 18,17</t>
+          <t>12,36; 18,03</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19,91; 26,61</t>
+          <t>19,88; 26,66</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22,31; 30,15</t>
+          <t>22,37; 30,27</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>17,55; 23,93</t>
+          <t>17,48; 23,82</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,51; 30,58</t>
+          <t>23,24; 30,34</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,02; 35,33</t>
+          <t>27,59; 34,97</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>34,37; 75,65</t>
+          <t>34,14; 75,66</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>15,19; 19,71</t>
+          <t>15,26; 19,65</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18,78; 23,5</t>
+          <t>19,0; 23,71</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24,77; 29,8</t>
+          <t>24,8; 29,92</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>29,98; 63,29</t>
+          <t>29,98; 62,68</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>16,01; 21,53</t>
+          <t>15,89; 21,86</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>20,75; 27,31</t>
+          <t>20,8; 27,48</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13,39; 18,63</t>
+          <t>13,32; 18,57</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,83; 19,24</t>
+          <t>6,07; 19,24</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>22,93; 28,99</t>
+          <t>22,98; 29,26</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>28,55; 35,43</t>
+          <t>28,61; 35,33</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,45; 29,48</t>
+          <t>22,68; 29,08</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>26,74; 32,76</t>
+          <t>26,75; 32,75</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>20,26; 24,45</t>
+          <t>20,21; 24,53</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>25,8; 30,81</t>
+          <t>25,83; 30,56</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18,77; 23,12</t>
+          <t>18,98; 23,16</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>12,59; 24,75</t>
+          <t>11,55; 24,64</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>16,88; 19,62</t>
+          <t>16,92; 19,63</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>17,5; 20,28</t>
+          <t>17,54; 20,31</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>17,35; 19,91</t>
+          <t>17,31; 20,05</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>19,57; 27,47</t>
+          <t>19,41; 27,38</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>27,56; 30,67</t>
+          <t>27,64; 30,85</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>29,71; 33,12</t>
+          <t>29,8; 33,02</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>27,35; 30,48</t>
+          <t>27,23; 30,42</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>35,8; 50,77</t>
+          <t>35,95; 51,69</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>22,75; 24,87</t>
+          <t>22,7; 24,79</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>24,18; 26,34</t>
+          <t>24,14; 26,26</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>22,75; 24,91</t>
+          <t>22,87; 24,97</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>29,64; 40,15</t>
+          <t>29,65; 38,99</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que el dolor le dificultó su trabajo habitual las últimas 4 semanas</t>
+          <t>Población a la que el dolor le dificultó su trabajo habitual las últimas 4 semanas (tasa de respuesta: 99,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>52868; 82804</t>
+          <t>52745; 80480</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>46690; 75649</t>
+          <t>47068; 74666</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>46268; 74845</t>
+          <t>46547; 74495</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>73158; 110083</t>
+          <t>73545; 111519</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>77023; 108193</t>
+          <t>76566; 107013</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>87404; 123645</t>
+          <t>88076; 122505</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>92706; 126840</t>
+          <t>91398; 125554</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>130539; 159740</t>
+          <t>131476; 160235</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>137885; 180899</t>
+          <t>136715; 180751</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>144352; 188175</t>
+          <t>145077; 187669</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>145580; 190601</t>
+          <t>146440; 191139</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>215188; 262672</t>
+          <t>213678; 260388</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>88933; 128439</t>
+          <t>88590; 125970</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>56137; 92717</t>
+          <t>56781; 91484</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>51823; 81978</t>
+          <t>51273; 80495</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>100481; 143628</t>
+          <t>97906; 144015</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>188689; 233349</t>
+          <t>191655; 232819</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>132362; 174629</t>
+          <t>132413; 176267</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>94005; 133215</t>
+          <t>93280; 133247</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>159068; 197853</t>
+          <t>160517; 197495</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>288505; 347420</t>
+          <t>286856; 348163</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>195006; 250380</t>
+          <t>198874; 253679</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>154428; 202433</t>
+          <t>153589; 205552</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>271816; 329277</t>
+          <t>269480; 329199</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>31337; 54250</t>
+          <t>31236; 55679</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>38264; 67099</t>
+          <t>38867; 68021</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>31537; 54430</t>
+          <t>31625; 53168</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>88350; 119205</t>
+          <t>87074; 119751</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>73752; 106140</t>
+          <t>75684; 107503</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>74326; 106884</t>
+          <t>73589; 108065</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>58815; 90978</t>
+          <t>61776; 93492</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>112991; 143627</t>
+          <t>112433; 141761</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>112782; 154814</t>
+          <t>109953; 152907</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>120085; 163463</t>
+          <t>122880; 164683</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>97410; 137924</t>
+          <t>98779; 136978</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>210509; 254632</t>
+          <t>209006; 251495</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>60277; 93138</t>
+          <t>59569; 90007</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>47356; 76239</t>
+          <t>50495; 79141</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>67106; 99040</t>
+          <t>66308; 98840</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>78488; 118124</t>
+          <t>78759; 115557</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>111271; 147828</t>
+          <t>112434; 148861</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>115705; 153270</t>
+          <t>116355; 153460</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>124402; 164514</t>
+          <t>125077; 165978</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>97103; 207840</t>
+          <t>101294; 207197</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>181763; 233023</t>
+          <t>179884; 227982</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>171997; 220699</t>
+          <t>173760; 223456</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>201175; 250923</t>
+          <t>200725; 251421</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>184167; 306324</t>
+          <t>190267; 302812</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>22309; 40901</t>
+          <t>22267; 43460</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>34430; 59393</t>
+          <t>34043; 59097</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>34484; 58789</t>
+          <t>34147; 59042</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>34730; 51959</t>
+          <t>33880; 51645</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>35638; 61435</t>
+          <t>36946; 61768</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>86268; 116041</t>
+          <t>87685; 117670</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>51720; 78153</t>
+          <t>50892; 78539</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>60570; 78833</t>
+          <t>60889; 79107</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>64180; 96541</t>
+          <t>64050; 94870</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>128800; 167627</t>
+          <t>127305; 167846</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>91048; 127288</t>
+          <t>92685; 128927</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>99603; 124764</t>
+          <t>99394; 124479</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>39317; 65207</t>
+          <t>40485; 63732</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>54353; 81449</t>
+          <t>53339; 81538</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>46477; 74235</t>
+          <t>45275; 71969</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>104077; 132572</t>
+          <t>104363; 132622</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>66464; 98477</t>
+          <t>68962; 99018</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>66581; 97325</t>
+          <t>65963; 95583</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>68100; 99591</t>
+          <t>68633; 100141</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>126765; 153581</t>
+          <t>127633; 153419</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>115349; 154794</t>
+          <t>114628; 154084</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>128924; 172995</t>
+          <t>130523; 170224</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>122737; 163212</t>
+          <t>121151; 162354</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>238424; 277924</t>
+          <t>238171; 275755</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>68768; 103415</t>
+          <t>70553; 103279</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>81221; 120259</t>
+          <t>81823; 119338</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>129339; 172894</t>
+          <t>129139; 173210</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>139097; 187974</t>
+          <t>139492; 188731</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>112023; 152699</t>
+          <t>111547; 152000</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>162878; 211901</t>
+          <t>161018; 210223</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>192827; 243133</t>
+          <t>189866; 240631</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>291251; 641102</t>
+          <t>289305; 641209</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>190318; 247073</t>
+          <t>191302; 246281</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>254392; 318402</t>
+          <t>257422; 321159</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>331393; 398715</t>
+          <t>331833; 400248</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>441083; 930988</t>
+          <t>440996; 922056</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>119084; 160119</t>
+          <t>118202; 162606</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>160598; 211419</t>
+          <t>160972; 212677</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>103697; 144259</t>
+          <t>103140; 143833</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>54094; 178518</t>
+          <t>56310; 178554</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>179698; 227126</t>
+          <t>180067; 229286</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>235205; 291914</t>
+          <t>235679; 291091</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>184597; 242326</t>
+          <t>186481; 239055</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>191577; 234729</t>
+          <t>191631; 234660</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>309406; 373418</t>
+          <t>308739; 374636</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>412314; 492350</t>
+          <t>412743; 488327</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>299730; 369190</t>
+          <t>303088; 369811</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>207052; 407041</t>
+          <t>189927; 405205</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>552983; 642865</t>
+          <t>554337; 643076</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>596618; 691523</t>
+          <t>597889; 692568</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>584514; 670850</t>
+          <t>583392; 675663</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>676549; 949686</t>
+          <t>670918; 946553</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>931344; 1036340</t>
+          <t>933971; 1042379</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1056150; 1177238</t>
+          <t>1059235; 1173836</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>963266; 1073617</t>
+          <t>959073; 1071321</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>1309506; 1857299</t>
+          <t>1314973; 1891058</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1514374; 1655188</t>
+          <t>1510899; 1649700</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1684174; 1834398</t>
+          <t>1681452; 1828983</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1567702; 1716472</t>
+          <t>1576319; 1720911</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>2109118; 2856413</t>
+          <t>2109545; 2774079</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P11_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P11_R-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>50,35%</t>
+          <t>48,99%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>38,55%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>19,32; 29,48</t>
+          <t>18,82; 29,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16,14; 25,6</t>
+          <t>16,28; 25,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16,08; 25,73</t>
+          <t>15,68; 25,71</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23,61; 35,81</t>
+          <t>23,89; 33,52</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>29,35; 41,03</t>
+          <t>29,39; 41,67</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,76; 42,79</t>
+          <t>31,04; 43,08</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,86; 43,77</t>
+          <t>32,1; 43,65</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>45,39; 55,32</t>
+          <t>43,81; 53,51</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>25,61; 33,86</t>
+          <t>25,65; 33,98</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25,1; 32,47</t>
+          <t>24,73; 33,16</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25,41; 33,16</t>
+          <t>25,3; 32,75</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>35,55; 43,32</t>
+          <t>35,36; 41,96</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>29,11%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>17,97; 25,55</t>
+          <t>18,13; 25,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,25; 18,13</t>
+          <t>11,22; 18,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,2; 16,02</t>
+          <t>10,2; 15,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18,89; 27,78</t>
+          <t>19,73; 28,21</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>38,03; 46,2</t>
+          <t>37,84; 46,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,28; 33,65</t>
+          <t>24,95; 33,36</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,94; 25,63</t>
+          <t>18,1; 25,93</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>31,17; 38,35</t>
+          <t>30,84; 38,06</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>28,77; 34,92</t>
+          <t>29,21; 34,83</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19,34; 24,67</t>
+          <t>19,26; 24,6</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15,02; 20,1</t>
+          <t>14,92; 19,88</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>26,08; 31,86</t>
+          <t>26,45; 32,15</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>36,59%</t>
+          <t>36,92%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>35,27%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,8; 17,46</t>
+          <t>9,65; 16,69</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,99; 20,99</t>
+          <t>12,09; 20,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,01; 16,83</t>
+          <t>10,2; 17,55</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>27,55; 37,89</t>
+          <t>28,86; 38,88</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>22,56; 32,05</t>
+          <t>22,55; 32,19</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21,58; 31,69</t>
+          <t>21,48; 31,33</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,65; 28,23</t>
+          <t>18,08; 27,83</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>32,2; 40,6</t>
+          <t>32,68; 41,35</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16,81; 23,37</t>
+          <t>17,07; 23,26</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18,48; 24,76</t>
+          <t>18,12; 24,88</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15,26; 21,17</t>
+          <t>15,33; 21,45</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>31,42; 37,81</t>
+          <t>32,01; 38,6</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>43,42%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>36,92%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,61; 25,09</t>
+          <t>16,34; 25,34</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,73; 21,52</t>
+          <t>12,87; 21,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,02; 26,86</t>
+          <t>18,32; 27,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25,31; 37,14</t>
+          <t>24,28; 35,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>30,27; 40,08</t>
+          <t>30,72; 39,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,07; 39,65</t>
+          <t>30,12; 39,76</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,55; 43,2</t>
+          <t>31,81; 42,35</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>21,31; 43,6</t>
+          <t>39,38; 48,32</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>24,64; 31,23</t>
+          <t>24,93; 31,29</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>23,02; 29,6</t>
+          <t>22,85; 29,34</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26,69; 33,43</t>
+          <t>26,56; 33,46</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>24,19; 38,51</t>
+          <t>32,97; 40,46</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>27,39%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,95; 21,38</t>
+          <t>10,74; 20,29</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,01; 27,79</t>
+          <t>16,57; 27,65</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16,54; 28,6</t>
+          <t>16,65; 27,73</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18,95; 28,89</t>
+          <t>18,19; 27,39</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>17,79; 29,74</t>
+          <t>17,73; 29,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>39,93; 53,59</t>
+          <t>39,6; 53,38</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,28; 35,93</t>
+          <t>23,23; 35,44</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>29,24; 37,99</t>
+          <t>28,01; 35,89</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>15,58; 23,08</t>
+          <t>15,67; 23,55</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29,45; 38,83</t>
+          <t>29,56; 38,7</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21,81; 30,33</t>
+          <t>21,49; 29,9</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>25,69; 32,17</t>
+          <t>24,35; 30,66</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>54,74%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>48,96%</t>
+          <t>49,15%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14,95; 23,53</t>
+          <t>14,63; 24,36</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>19,53; 29,86</t>
+          <t>19,83; 30,35</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17,21; 27,35</t>
+          <t>17,21; 27,22</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>38,71; 49,19</t>
+          <t>38,55; 48,96</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>24,79; 35,6</t>
+          <t>24,37; 35,17</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>23,56; 34,13</t>
+          <t>24,16; 34,62</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>25,33; 36,96</t>
+          <t>25,29; 36,25</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>49,65; 59,68</t>
+          <t>49,41; 59,71</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>20,88; 28,07</t>
+          <t>21,0; 28,23</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>23,6; 30,77</t>
+          <t>23,23; 30,81</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>22,68; 30,4</t>
+          <t>22,41; 30,42</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>45,22; 52,36</t>
+          <t>45,29; 52,64</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>50,84%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>31,17%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>11,47; 16,79</t>
+          <t>11,37; 16,92</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12,36; 18,03</t>
+          <t>12,41; 18,38</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19,88; 26,66</t>
+          <t>19,77; 26,57</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22,37; 30,27</t>
+          <t>23,37; 30,53</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>17,48; 23,82</t>
+          <t>17,64; 23,77</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,24; 30,34</t>
+          <t>23,06; 30,49</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,59; 34,97</t>
+          <t>27,72; 35,39</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>34,14; 75,66</t>
+          <t>31,98; 38,24</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>15,26; 19,65</t>
+          <t>15,18; 19,33</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19,0; 23,71</t>
+          <t>18,74; 23,43</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24,8; 29,92</t>
+          <t>24,92; 30,06</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>29,98; 62,68</t>
+          <t>28,75; 33,59</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>23,66%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>15,89; 21,86</t>
+          <t>15,99; 21,71</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>20,8; 27,48</t>
+          <t>21,05; 27,24</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13,32; 18,57</t>
+          <t>13,43; 18,66</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6,07; 19,24</t>
+          <t>15,66; 21,17</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>22,98; 29,26</t>
+          <t>22,8; 29,36</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>28,61; 35,33</t>
+          <t>28,38; 35,21</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,68; 29,08</t>
+          <t>22,73; 29,05</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>26,75; 32,75</t>
+          <t>26,31; 31,58</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>20,21; 24,53</t>
+          <t>20,34; 24,53</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>25,83; 30,56</t>
+          <t>25,73; 30,4</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18,98; 23,16</t>
+          <t>19,07; 23,45</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>11,55; 24,64</t>
+          <t>22,05; 25,74</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>31,93%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>16,92; 19,63</t>
+          <t>16,88; 19,53</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>17,54; 20,31</t>
+          <t>17,52; 20,32</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>17,31; 20,05</t>
+          <t>17,39; 20,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>19,41; 27,38</t>
+          <t>24,8; 27,94</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>27,64; 30,85</t>
+          <t>27,78; 30,92</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>29,8; 33,02</t>
+          <t>29,68; 32,79</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>27,23; 30,42</t>
+          <t>27,19; 30,24</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>35,95; 51,69</t>
+          <t>35,69; 38,47</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>22,7; 24,79</t>
+          <t>22,66; 24,77</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>24,14; 26,26</t>
+          <t>24,22; 26,34</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>22,87; 24,97</t>
+          <t>22,78; 24,83</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>29,65; 38,99</t>
+          <t>30,92; 33,08</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>91127</t>
+          <t>89913</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>145839</t>
+          <t>154836</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>236965</t>
+          <t>244750</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>52745; 80480</t>
+          <t>51383; 80758</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>47068; 74666</t>
+          <t>47473; 75026</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>46547; 74495</t>
+          <t>45403; 74424</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>73545; 111519</t>
+          <t>76179; 106865</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>76566; 107013</t>
+          <t>76655; 108682</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>88076; 122505</t>
+          <t>88863; 123342</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>91398; 125554</t>
+          <t>92065; 125209</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>131476; 160235</t>
+          <t>138463; 169126</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>136715; 180751</t>
+          <t>136949; 181378</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>145077; 187669</t>
+          <t>142952; 191638</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>146440; 191139</t>
+          <t>145815; 188776</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>213678; 260388</t>
+          <t>224492; 266385</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>120429</t>
+          <t>126195</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>178783</t>
+          <t>187404</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>299211</t>
+          <t>313599</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>88590; 125970</t>
+          <t>89392; 126175</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>56781; 91484</t>
+          <t>56637; 92063</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>51273; 80495</t>
+          <t>51277; 79827</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>97906; 144015</t>
+          <t>104679; 149716</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>191655; 232819</t>
+          <t>190692; 232468</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>132413; 176267</t>
+          <t>130693; 174710</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>93280; 133247</t>
+          <t>94074; 134784</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>160517; 197495</t>
+          <t>168565; 207991</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>286856; 348163</t>
+          <t>291263; 347261</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>198874; 253679</t>
+          <t>198095; 252949</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>153589; 205552</t>
+          <t>152589; 203252</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>269480; 329199</t>
+          <t>284875; 346334</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>103064</t>
+          <t>105584</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>127741</t>
+          <t>131569</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>230806</t>
+          <t>237153</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>31236; 55679</t>
+          <t>30772; 53207</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>38867; 68021</t>
+          <t>39179; 66168</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>31625; 53168</t>
+          <t>32215; 55445</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>87074; 119751</t>
+          <t>91202; 122853</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>75684; 107503</t>
+          <t>75652; 107967</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>73589; 108065</t>
+          <t>73255; 106835</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>61776; 93492</t>
+          <t>59883; 92179</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>112433; 141761</t>
+          <t>116470; 147357</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>109953; 152907</t>
+          <t>111669; 152148</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>122880; 164683</t>
+          <t>120516; 165456</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>98779; 136978</t>
+          <t>99192; 138832</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>209006; 251495</t>
+          <t>215232; 259553</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>96855</t>
+          <t>109833</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>164605</t>
+          <t>182991</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>261460</t>
+          <t>292824</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>59569; 90007</t>
+          <t>58624; 90887</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>50495; 79141</t>
+          <t>47350; 78247</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>66308; 98840</t>
+          <t>67403; 100159</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>78759; 115557</t>
+          <t>90221; 133325</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>112434; 148861</t>
+          <t>114130; 147878</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>116355; 153460</t>
+          <t>116580; 153865</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>125077; 165978</t>
+          <t>122241; 162713</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>101294; 207197</t>
+          <t>165958; 203641</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>179884; 227982</t>
+          <t>182056; 228491</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>173760; 223456</t>
+          <t>172453; 221433</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>200725; 251421</t>
+          <t>199748; 251693</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>190267; 302812</t>
+          <t>261475; 320845</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>42182</t>
+          <t>46345</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>69445</t>
+          <t>72089</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>111627</t>
+          <t>118434</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>22267; 43460</t>
+          <t>21834; 41261</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>34043; 59097</t>
+          <t>35231; 58786</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>34147; 59042</t>
+          <t>34367; 57260</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>33880; 51645</t>
+          <t>37416; 56334</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>36946; 61768</t>
+          <t>36825; 60674</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>87685; 117670</t>
+          <t>86964; 117215</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>50892; 78539</t>
+          <t>50778; 77462</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>60889; 79107</t>
+          <t>63518; 81391</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>64050; 94870</t>
+          <t>64407; 96778</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>127305; 167846</t>
+          <t>127744; 167249</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>92685; 128927</t>
+          <t>91333; 127071</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>99394; 124479</t>
+          <t>105295; 132561</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>117786</t>
+          <t>118278</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>140088</t>
+          <t>144384</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>257874</t>
+          <t>262661</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>40485; 63732</t>
+          <t>39617; 65962</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>53339; 81538</t>
+          <t>54145; 82890</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>45275; 71969</t>
+          <t>45275; 71615</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>104363; 132622</t>
+          <t>104349; 132552</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>68962; 99018</t>
+          <t>67770; 97827</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>65963; 95583</t>
+          <t>67668; 96947</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>68633; 100141</t>
+          <t>68539; 98241</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>127633; 153419</t>
+          <t>130328; 157474</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>114628; 154084</t>
+          <t>115272; 154968</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>130523; 170224</t>
+          <t>128514; 170415</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>121151; 162354</t>
+          <t>119667; 162452</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>238171; 275755</t>
+          <t>242048; 281363</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>163401</t>
+          <t>193093</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>430865</t>
+          <t>270983</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>594266</t>
+          <t>464076</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>70553; 103279</t>
+          <t>69942; 104059</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>81823; 119338</t>
+          <t>82113; 121629</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>129139; 173210</t>
+          <t>128430; 172595</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>139492; 188731</t>
+          <t>167922; 219438</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>111547; 152000</t>
+          <t>112577; 151701</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>161018; 210223</t>
+          <t>159767; 211240</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>189866; 240631</t>
+          <t>190784; 243526</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>289305; 641209</t>
+          <t>246262; 294467</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>191302; 246281</t>
+          <t>190211; 242311</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>257422; 321159</t>
+          <t>253881; 317473</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>331833; 400248</t>
+          <t>333395; 402191</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>440996; 922056</t>
+          <t>428080; 500110</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>124961</t>
+          <t>144071</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>213366</t>
+          <t>240838</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>338328</t>
+          <t>384909</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>118202; 162606</t>
+          <t>118905; 161480</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>160972; 212677</t>
+          <t>162954; 210847</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>103140; 143833</t>
+          <t>104008; 144550</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>56310; 178554</t>
+          <t>124841; 168710</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>180067; 229286</t>
+          <t>178635; 230064</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>235679; 291091</t>
+          <t>233821; 290079</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>186481; 239055</t>
+          <t>186877; 238858</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>191631; 234660</t>
+          <t>218354; 262092</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>308739; 374636</t>
+          <t>310583; 374583</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>412743; 488327</t>
+          <t>411181; 485702</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>303088; 369811</t>
+          <t>304493; 374356</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>189927; 405205</t>
+          <t>358671; 418746</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>859805</t>
+          <t>933312</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>1470732</t>
+          <t>1385094</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>2330537</t>
+          <t>2318406</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>554337; 643076</t>
+          <t>553244; 639974</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>597889; 692568</t>
+          <t>597213; 692784</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>583392; 675663</t>
+          <t>585906; 673772</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>670918; 946553</t>
+          <t>875133; 985944</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>933971; 1042379</t>
+          <t>938814; 1044684</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1059235; 1173836</t>
+          <t>1054956; 1165572</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>959073; 1071321</t>
+          <t>957490; 1065099</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>1314973; 1891058</t>
+          <t>1331342; 1435380</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1510899; 1649700</t>
+          <t>1508456; 1648796</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1681452; 1828983</t>
+          <t>1686514; 1834573</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1576319; 1720911</t>
+          <t>1570059; 1711007</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>2109545; 2774079</t>
+          <t>2244434; 2401930</t>
         </is>
       </c>
     </row>
